--- a/cameraCalibration/star/calibration_validation.xlsx
+++ b/cameraCalibration/star/calibration_validation.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">file</t>
   </si>
@@ -41,6 +41,12 @@
   </si>
   <si>
     <t xml:space="preserve">calc_y (cm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%e X</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%e Y</t>
   </si>
   <si>
     <t xml:space="preserve">cameraCalibration/star/0x400y.jpg</t>
@@ -119,11 +125,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="0.0000000"/>
+    <numFmt numFmtId="165" formatCode="0.00%"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -154,17 +161,27 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFC9211E"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="13"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -211,7 +228,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -220,11 +237,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -313,12 +350,20 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:rPr>
               <a:t>asdf</a:t>
             </a:r>
@@ -376,11 +421,16 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -418,11 +468,26 @@
                 <c:pt idx="5">
                   <c:v>120.2</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>120.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>120.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>120</c:v>
+                </c:pt>
                 <c:pt idx="9">
                   <c:v>14.9</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>144.2</c:v>
+                </c:pt>
                 <c:pt idx="11">
                   <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>258.4</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>34.7</c:v>
@@ -543,8 +608,8 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="68684009"/>
-        <c:axId val="89003843"/>
+        <c:axId val="1757095"/>
+        <c:axId val="29493979"/>
       </c:scatterChart>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
@@ -587,11 +652,16 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -629,11 +699,26 @@
                 <c:pt idx="5">
                   <c:v>400</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>678.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>423.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>602.7</c:v>
+                </c:pt>
                 <c:pt idx="9">
                   <c:v>1300</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>849.9</c:v>
+                </c:pt>
                 <c:pt idx="11">
                   <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>554.9</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1600</c:v>
@@ -754,11 +839,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="39424005"/>
-        <c:axId val="5271075"/>
+        <c:axId val="35608147"/>
+        <c:axId val="22466479"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="68684009"/>
+        <c:axId val="1757095"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -772,12 +857,175 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:rPr>
+                  <a:t>asdf</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="29493979"/>
+        <c:crosses val="min"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="29493979"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:solidFill>
+                <a:srgbClr val="b3b3b3"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:rPr>
+                  <a:t>X Axis, Hall Width (cm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="0">
+            <a:solidFill>
+              <a:srgbClr val="b3b3b3"/>
+            </a:solidFill>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1757095"/>
+        <c:crosses val="min"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="35608147"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="t"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>asdf</a:t>
                 </a:r>
@@ -809,31 +1057,25 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89003843"/>
-        <c:crosses val="min"/>
-        <c:crossBetween val="between"/>
+        <c:crossAx val="22466479"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="89003843"/>
+        <c:axId val="22466479"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="0">
-              <a:solidFill>
-                <a:srgbClr val="b3b3b3"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-        </c:majorGridlines>
+        <c:axPos val="r"/>
         <c:title>
           <c:tx>
             <c:rich>
@@ -842,14 +1084,22 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
-                  <a:t>X Axis, Hall Width (cm)</a:t>
+                  <a:t>Y Axis, Hall Width (cm)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -862,7 +1112,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -879,135 +1129,18 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68684009"/>
-        <c:crosses val="min"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="39424005"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="t"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>asdf</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
-            </a:solidFill>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="5271075"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="5271075"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="r"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
-                    <a:latin typeface="Arial"/>
-                  </a:rPr>
-                  <a:t>Y Axis, Hall Width (cm)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln w="0">
-              <a:noFill/>
-            </a:ln>
-          </c:spPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:ln w="0">
-            <a:solidFill>
-              <a:srgbClr val="b3b3b3"/>
-            </a:solidFill>
-          </a:ln>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
-                <a:latin typeface="Arial"/>
-              </a:defRPr>
-            </a:pPr>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="39424005"/>
+        <c:crossAx val="35608147"/>
         <c:crosses val="max"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1033,7 +1166,11 @@
         <a:p>
           <a:pPr>
             <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
               <a:latin typeface="Arial"/>
+              <a:ea typeface="DejaVu Sans"/>
             </a:defRPr>
           </a:pPr>
         </a:p>
@@ -1066,12 +1203,20 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:rPr>
               <a:t>Distance Across Hall
 Generated from: calibrator.pixle_to_meters</a:t>
@@ -1083,7 +1228,7 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.360444777611194"/>
+          <c:x val="0.360462211118051"/>
           <c:y val="0"/>
         </c:manualLayout>
       </c:layout>
@@ -1102,10 +1247,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.134441181982882"/>
+          <c:x val="0.134415990006246"/>
           <c:y val="0.143095026642984"/>
-          <c:w val="0.827637908415069"/>
-          <c:h val="0.704706927175844"/>
+          <c:w val="0.827607745159276"/>
+          <c:h val="0.704595914742451"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -1149,11 +1294,16 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1205,11 +1355,26 @@
                 <c:pt idx="5">
                   <c:v>120.2</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>120.2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>120.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>120</c:v>
+                </c:pt>
                 <c:pt idx="9">
                   <c:v>14.9</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>144.2</c:v>
+                </c:pt>
                 <c:pt idx="11">
                   <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>258.4</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>34.7</c:v>
@@ -1330,11 +1495,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="7077866"/>
-        <c:axId val="28432829"/>
+        <c:axId val="27383517"/>
+        <c:axId val="89788688"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="7077866"/>
+        <c:axId val="27383517"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1348,12 +1513,20 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Read From Image Lable (cm)</a:t>
                 </a:r>
@@ -1368,7 +1541,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1385,17 +1558,21 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28432829"/>
-        <c:crossesAt val="0"/>
-        <c:crossBetween val="between"/>
+        <c:crossAx val="89788688"/>
+        <c:crosses val="min"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="28432829"/>
+        <c:axId val="89788688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1418,12 +1595,20 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Calculated From Image (cm)</a:t>
                 </a:r>
@@ -1438,7 +1623,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1455,14 +1640,18 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7077866"/>
+        <c:crossAx val="27383517"/>
         <c:crossesAt val="0"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1500,12 +1689,20 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
               <a:rPr b="0" sz="1300" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:rPr>
               <a:t>Distance Down Hall
 Generated from: calibrator.pixle_to_meters</a:t>
@@ -1517,8 +1714,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.360507246376812"/>
-          <c:y val="0.000222000222000222"/>
+          <c:x val="0.360529768226401"/>
+          <c:y val="0.00022202486678508"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -1536,10 +1733,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.134432783608196"/>
-          <c:y val="0.143079143079143"/>
-          <c:w val="0.827586206896552"/>
-          <c:h val="0.704628704628705"/>
+          <c:x val="0.134441181982883"/>
+          <c:y val="0.143095026642984"/>
+          <c:w val="0.827512963078653"/>
+          <c:h val="0.704595914742451"/>
         </c:manualLayout>
       </c:layout>
       <c:scatterChart>
@@ -1561,7 +1758,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="ff420e"/>
+              <a:srgbClr val="0000ff"/>
             </a:solidFill>
             <a:ln w="28800">
               <a:noFill/>
@@ -1572,22 +1769,63 @@
             <c:size val="8"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="ff420e"/>
+                <a:srgbClr val="0000ff"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
+          <c:dPt>
+            <c:idx val="21"/>
+            <c:marker>
+              <c:symbol val="diamond"/>
+              <c:size val="8"/>
+              <c:spPr>
+                <a:solidFill>
+                  <a:srgbClr val="0000ff"/>
+                </a:solidFill>
+              </c:spPr>
+            </c:marker>
+          </c:dPt>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="21"/>
+              <c:txPr>
+                <a:bodyPr wrap="none"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Arial"/>
+                    </a:defRPr>
+                  </a:pPr>
+                </a:p>
+              </c:txPr>
+              <c:dLblPos val="r"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:separator> </c:separator>
+            </c:dLbl>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1605,7 +1843,7 @@
             <c:spPr>
               <a:ln w="0">
                 <a:solidFill>
-                  <a:srgbClr val="ff420e"/>
+                  <a:srgbClr val="0000ff"/>
                 </a:solidFill>
               </a:ln>
             </c:spPr>
@@ -1639,11 +1877,26 @@
                 <c:pt idx="5">
                   <c:v>400</c:v>
                 </c:pt>
+                <c:pt idx="6">
+                  <c:v>678.7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>423.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>602.7</c:v>
+                </c:pt>
                 <c:pt idx="9">
                   <c:v>1300</c:v>
                 </c:pt>
+                <c:pt idx="10">
+                  <c:v>849.9</c:v>
+                </c:pt>
                 <c:pt idx="11">
                   <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>554.9</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>1600</c:v>
@@ -1764,11 +2017,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="74243457"/>
-        <c:axId val="39362478"/>
+        <c:axId val="93391871"/>
+        <c:axId val="52965435"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="74243457"/>
+        <c:axId val="93391871"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1782,12 +2035,20 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Read From Image Lable (cm)</a:t>
                 </a:r>
@@ -1802,7 +2063,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1819,17 +2080,21 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39362478"/>
+        <c:crossAx val="52965435"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="39362478"/>
+        <c:axId val="52965435"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1852,12 +2117,20 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
                   <a:rPr b="0" sz="900" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
+                    <a:ea typeface="DejaVu Sans"/>
                   </a:rPr>
                   <a:t>Calculated From Image (cm)</a:t>
                 </a:r>
@@ -1872,7 +2145,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="General" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1889,14 +2162,18 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:latin typeface="Arial"/>
+                <a:ea typeface="DejaVu Sans"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74243457"/>
+        <c:crossAx val="93391871"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1932,9 +2209,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>37440</xdr:colOff>
+      <xdr:colOff>37080</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>110160</xdr:rowOff>
+      <xdr:rowOff>109800</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1942,8 +2219,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="10742040" y="284400"/>
-        <a:ext cx="5759640" cy="3239640"/>
+        <a:off x="10743120" y="284400"/>
+        <a:ext cx="5759640" cy="3239280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1962,9 +2239,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1208880</xdr:colOff>
+      <xdr:colOff>1208520</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>77040</xdr:rowOff>
+      <xdr:rowOff>76680</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1973,7 +2250,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="590040" y="4637160"/>
-        <a:ext cx="5762520" cy="3242880"/>
+        <a:ext cx="5763240" cy="3242520"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1992,9 +2269,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>140040</xdr:colOff>
+      <xdr:colOff>139680</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>43200</xdr:rowOff>
+      <xdr:rowOff>42840</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2002,8 +2279,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6777720" y="4440600"/>
-        <a:ext cx="5762520" cy="3242880"/>
+        <a:off x="6779160" y="4440600"/>
+        <a:ext cx="5762160" cy="3242520"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2127,7 +2404,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="33.37"/>
@@ -2135,6 +2412,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="10.75"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="17.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.58"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="8" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="9" min="9" style="3" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2159,79 +2438,109 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1" t="n">
+      <c r="A2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="4" t="n">
         <v>948</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2" s="4" t="n">
         <v>1481</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2" s="4" t="n">
         <v>-5.86669355542368</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="4" t="n">
         <v>402.045385469408</v>
+      </c>
+      <c r="H2" s="5" t="e">
+        <f aca="false">(F2-B2)/B2</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <f aca="false">(G2-C2)/C2</f>
+        <v>0.00511346367352005</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1" t="n">
+      <c r="A3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="4" t="n">
         <v>800</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="4" t="n">
         <v>1109</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3" s="4" t="n">
         <v>790</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" s="4" t="n">
         <v>-7.96943433811734</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="4" t="n">
         <v>802.621278846541</v>
+      </c>
+      <c r="H3" s="5" t="e">
+        <f aca="false">(F3-B3)/B3</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <f aca="false">(G3-C3)/C3</f>
+        <v>0.00327659855817629</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="n">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="4" t="n">
         <v>900</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="4" t="n">
         <v>1133</v>
       </c>
-      <c r="E4" s="1" t="n">
+      <c r="E4" s="4" t="n">
         <v>703</v>
       </c>
-      <c r="F4" s="1" t="n">
+      <c r="F4" s="4" t="n">
         <v>-6.94949659190636</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="4" t="n">
         <v>902.135708207518</v>
+      </c>
+      <c r="H4" s="5" t="e">
+        <f aca="false">(F4-B4)/B4</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <f aca="false">(G4-C4)/C4</f>
+        <v>0.00237300911946439</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>108.3</v>
@@ -2250,11 +2559,19 @@
       </c>
       <c r="G5" s="1" t="n">
         <v>496.262057292665</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <f aca="false">(F5-B5)/B5</f>
+        <v>-0.0163269442484395</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <f aca="false">(G5-C5)/C5</f>
+        <v>-0.00747588541466996</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>120.1</v>
@@ -2274,33 +2591,55 @@
       <c r="G6" s="1" t="n">
         <v>1983.39406724609</v>
       </c>
+      <c r="H6" s="2" t="n">
+        <f aca="false">(F6-B6)/B6</f>
+        <v>0.0058980193721816</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <f aca="false">(G6-C6)/C6</f>
+        <v>-0.00830296637695506</v>
+      </c>
     </row>
-    <row r="7" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="2" t="n">
+    <row r="7" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="4" t="n">
         <v>120.2</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="4" t="n">
         <v>400</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="4" t="n">
         <v>1683</v>
       </c>
-      <c r="E7" s="2" t="n">
+      <c r="E7" s="4" t="n">
         <v>1485</v>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="4" t="n">
         <v>150.165934068324</v>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="4" t="n">
         <v>395.826762032533</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <f aca="false">(F7-B7)/B7</f>
+        <v>0.249300616209018</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <f aca="false">(G7-C7)/C7</f>
+        <v>-0.0104330949186675</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>120.2</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>678.7</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>1472</v>
@@ -2314,27 +2653,55 @@
       <c r="G8" s="1" t="n">
         <v>677.022670688424</v>
       </c>
+      <c r="H8" s="2" t="n">
+        <f aca="false">(F8-B8)/B8</f>
+        <v>0.0114259891181946</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <f aca="false">(G8-C8)/C8</f>
+        <v>-0.00247138545981442</v>
+      </c>
     </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="1" t="n">
+    <row r="9" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>120.7</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>423.8</v>
+      </c>
+      <c r="D9" s="4" t="n">
         <v>1672</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="E9" s="4" t="n">
         <v>1422</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="F9" s="4" t="n">
         <v>150.86589603219</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="4" t="n">
         <v>417.367797921966</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <f aca="false">(F9-B9)/B9</f>
+        <v>0.249924573588981</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <f aca="false">(G9-C9)/C9</f>
+        <v>-0.0151774470930487</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>602.7</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>1479</v>
@@ -2348,33 +2715,55 @@
       <c r="G10" s="1" t="n">
         <v>599.749054319427</v>
       </c>
+      <c r="H10" s="2" t="n">
+        <f aca="false">(F10-B10)/B10</f>
+        <v>-0.00769136514575</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <f aca="false">(G10-C10)/C10</f>
+        <v>-0.0048962098566003</v>
+      </c>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="1" t="n">
+    <row r="11" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="4" t="n">
         <v>14.9</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="4" t="n">
         <v>1300</v>
       </c>
-      <c r="D11" s="1" t="n">
+      <c r="D11" s="4" t="n">
         <v>1221</v>
       </c>
-      <c r="E11" s="1" t="n">
+      <c r="E11" s="4" t="n">
         <v>477</v>
       </c>
-      <c r="F11" s="1" t="n">
+      <c r="F11" s="4" t="n">
         <v>11.9710014462234</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="4" t="n">
         <v>1302.65352559053</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <f aca="false">(F11-B11)/B11</f>
+        <v>-0.196577084146081</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <f aca="false">(G11-C11)/C11</f>
+        <v>0.00204117353117698</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>144.2</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>849.9</v>
       </c>
       <c r="D12" s="1" t="n">
         <v>1507</v>
@@ -2388,188 +2777,266 @@
       <c r="G12" s="1" t="n">
         <v>843.632908434815</v>
       </c>
+      <c r="H12" s="2" t="n">
+        <f aca="false">(F12-B12)/B12</f>
+        <v>0.00846097859347443</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <f aca="false">(G12-C12)/C12</f>
+        <v>-0.00737391641979639</v>
+      </c>
     </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="1" t="n">
+    <row r="13" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="4" t="n">
         <v>19.5</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="4" t="n">
         <v>1000</v>
       </c>
-      <c r="D13" s="1" t="n">
+      <c r="D13" s="4" t="n">
         <v>1201</v>
       </c>
-      <c r="E13" s="1" t="n">
+      <c r="E13" s="4" t="n">
         <v>631</v>
       </c>
-      <c r="F13" s="1" t="n">
+      <c r="F13" s="4" t="n">
         <v>16.0058034383993</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="G13" s="4" t="n">
         <v>1002.99389046401</v>
       </c>
+      <c r="H13" s="5" t="n">
+        <f aca="false">(F13-B13)/B13</f>
+        <v>-0.179189567261574</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <f aca="false">(G13-C13)/C13</f>
+        <v>0.00299389046400995</v>
+      </c>
     </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="1" t="n">
+    <row r="14" s="6" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>258.4</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>554.9</v>
+      </c>
+      <c r="D14" s="4" t="n">
         <v>1716</v>
       </c>
-      <c r="E14" s="1" t="n">
+      <c r="E14" s="4" t="n">
         <v>1122</v>
       </c>
-      <c r="F14" s="1" t="n">
+      <c r="F14" s="4" t="n">
         <v>182.170724260734</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="G14" s="4" t="n">
         <v>550.078896779978</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <f aca="false">(F14-B14)/B14</f>
+        <v>-0.295004937071463</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <f aca="false">(G14-C14)/C14</f>
+        <v>-0.0086882379167814</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="1" t="n">
+      <c r="A15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="7" t="n">
         <v>34.7</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="7" t="n">
         <v>1600</v>
       </c>
-      <c r="D15" s="1" t="n">
+      <c r="D15" s="7" t="n">
         <v>1269</v>
       </c>
-      <c r="E15" s="1" t="n">
+      <c r="E15" s="7" t="n">
         <v>379</v>
       </c>
-      <c r="F15" s="1" t="n">
+      <c r="F15" s="7" t="n">
         <v>32.6948954065275</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="G15" s="7" t="n">
         <v>1596.05420060739</v>
+      </c>
+      <c r="H15" s="8" t="n">
+        <f aca="false">(F15-B15)/B15</f>
+        <v>-0.0577839940481989</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <f aca="false">(G15-C15)/C15</f>
+        <v>-0.00246612462038129</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="1" t="n">
+      <c r="A16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="7" t="n">
         <v>36.2</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="7" t="n">
         <v>1400</v>
       </c>
-      <c r="D16" s="1" t="n">
+      <c r="D16" s="7" t="n">
         <v>1265</v>
       </c>
-      <c r="E16" s="1" t="n">
+      <c r="E16" s="7" t="n">
         <v>440</v>
       </c>
-      <c r="F16" s="1" t="n">
+      <c r="F16" s="7" t="n">
         <v>34.9433019600952</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="G16" s="7" t="n">
         <v>1401.62845844916</v>
+      </c>
+      <c r="H16" s="8" t="n">
+        <f aca="false">(F16-B16)/B16</f>
+        <v>-0.0347154154669836</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <f aca="false">(G16-C16)/C16</f>
+        <v>0.00116318460654286</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="1" t="n">
+      <c r="A17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="7" t="n">
         <v>45.1</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="7" t="n">
         <v>1200</v>
       </c>
-      <c r="D17" s="1" t="n">
+      <c r="D17" s="7" t="n">
         <v>1268</v>
       </c>
-      <c r="E17" s="1" t="n">
+      <c r="E17" s="7" t="n">
         <v>521</v>
       </c>
-      <c r="F17" s="1" t="n">
+      <c r="F17" s="7" t="n">
         <v>41.7308000406673</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="G17" s="7" t="n">
         <v>1202.9314368296</v>
+      </c>
+      <c r="H17" s="8" t="n">
+        <f aca="false">(F17-B17)/B17</f>
+        <v>-0.0747050988765566</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <f aca="false">(G17-C17)/C17</f>
+        <v>0.00244286402466666</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="1" t="n">
+      <c r="A18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="7" t="n">
         <v>48.8</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="7" t="n">
         <v>1700</v>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D18" s="7" t="n">
         <v>1291</v>
       </c>
-      <c r="E18" s="1" t="n">
+      <c r="E18" s="7" t="n">
         <v>354</v>
       </c>
-      <c r="F18" s="1" t="n">
+      <c r="F18" s="7" t="n">
         <v>46.6662521817725</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="G18" s="7" t="n">
         <v>1692.17155270141</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <f aca="false">(F18-B18)/B18</f>
+        <v>-0.0437243405374487</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <f aca="false">(G18-C18)/C18</f>
+        <v>-0.00460496899917055</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="1" t="n">
+      <c r="A19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="7" t="n">
         <v>52.9</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="7" t="n">
         <v>700</v>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D19" s="7" t="n">
         <v>1255</v>
       </c>
-      <c r="E19" s="1" t="n">
+      <c r="E19" s="7" t="n">
         <v>900</v>
       </c>
-      <c r="F19" s="1" t="n">
+      <c r="F19" s="7" t="n">
         <v>49.7948451179619</v>
       </c>
-      <c r="G19" s="1" t="n">
+      <c r="G19" s="7" t="n">
         <v>701.412086330138</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <f aca="false">(F19-B19)/B19</f>
+        <v>-0.0586985800007202</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <f aca="false">(G19-C19)/C19</f>
+        <v>0.0020172661859114</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="1" t="n">
+      <c r="A20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="7" t="n">
         <v>400</v>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D20" s="7" t="n">
         <v>1231</v>
       </c>
-      <c r="E20" s="1" t="n">
+      <c r="E20" s="7" t="n">
         <v>1482</v>
       </c>
-      <c r="F20" s="1" t="n">
+      <c r="F20" s="7" t="n">
         <v>53.7894234189463</v>
       </c>
-      <c r="G20" s="1" t="n">
+      <c r="G20" s="7" t="n">
         <v>399.844360480273</v>
+      </c>
+      <c r="H20" s="8" t="n">
+        <f aca="false">(F20-B20)/B20</f>
+        <v>-0.0563259049307667</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <f aca="false">(G20-C20)/C20</f>
+        <v>-0.000389098799317509</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="n">
         <v>63.5</v>
@@ -2589,33 +3056,49 @@
       <c r="G21" s="1" t="n">
         <v>1791.04614276847</v>
       </c>
+      <c r="H21" s="2" t="n">
+        <f aca="false">(F21-B21)/B21</f>
+        <v>0.00698906987495121</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <f aca="false">(G21-C21)/C21</f>
+        <v>-0.0049743651286278</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B22" s="1" t="n">
+      <c r="A22" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="7" t="n">
         <v>70.9</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="7" t="n">
         <v>1900</v>
       </c>
-      <c r="D22" s="1" t="n">
+      <c r="D22" s="7" t="n">
         <v>1321</v>
       </c>
-      <c r="E22" s="1" t="n">
+      <c r="E22" s="7" t="n">
         <v>310</v>
       </c>
-      <c r="F22" s="1" t="n">
+      <c r="F22" s="7" t="n">
         <v>68.3459865572016</v>
       </c>
-      <c r="G22" s="1" t="n">
+      <c r="G22" s="7" t="n">
         <v>1890.08898319521</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <f aca="false">(F22-B22)/B22</f>
+        <v>-0.0360227565980029</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <f aca="false">(G22-C22)/C22</f>
+        <v>-0.00521632463410003</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="n">
         <v>88.4</v>
@@ -2634,11 +3117,19 @@
       </c>
       <c r="G23" s="1" t="n">
         <v>1491.75425781505</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <f aca="false">(F23-B23)/B23</f>
+        <v>-0.00357106689615612</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <f aca="false">(G23-C23)/C23</f>
+        <v>-0.00549716145663327</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="n">
         <v>88.9</v>
@@ -2657,11 +3148,19 @@
       </c>
       <c r="G24" s="1" t="n">
         <v>799.912947939294</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <f aca="false">(F24-B24)/B24</f>
+        <v>-0.0113371918495152</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <f aca="false">(G24-C24)/C24</f>
+        <v>-0.000108815075882518</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="n">
         <v>90.6</v>
@@ -2680,6 +3179,14 @@
       </c>
       <c r="G25" s="1" t="n">
         <v>1100.17750794812</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <f aca="false">(F25-B25)/B25</f>
+        <v>-0.00350171716746688</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <f aca="false">(G25-C25)/C25</f>
+        <v>0.000161370861927191</v>
       </c>
     </row>
   </sheetData>
